--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -498,12 +498,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -512,29 +512,29 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>225</v>
+        <v>118.5</v>
       </c>
       <c r="E2" t="n">
-        <v>236.26</v>
+        <v>117.63</v>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>🔴 毛利34.58%跌破51%</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>🟡 賠率1.00 考慮減碼</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>🟠 賠率0.62&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
@@ -545,12 +545,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118.5</v>
+        <v>99.5</v>
       </c>
       <c r="E3" t="n">
-        <v>117.63</v>
+        <v>111.6</v>
       </c>
       <c r="F3" t="n">
         <v>130</v>
@@ -570,22 +570,14 @@
       <c r="G3" t="n">
         <v>100</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>🔴 毛利33.53%跌破44%</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.62&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
-        </is>
-      </c>
+          <t>🔴 跌破停損價100(現價99.5)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
@@ -639,47 +631,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>315</v>
+        <v>225</v>
       </c>
       <c r="E5" t="n">
-        <v>305.63</v>
+        <v>236.26</v>
       </c>
       <c r="F5" t="n">
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="G5" t="n">
-        <v>300</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>🔴 毛利31.33%跌破50%</t>
-        </is>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.67 考慮減碼</t>
+          <t>🟡 賠率1.00 考慮減碼</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
     </row>
@@ -772,41 +760,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99.5</v>
+        <v>315</v>
       </c>
       <c r="E8" t="n">
-        <v>111.6</v>
+        <v>305.63</v>
       </c>
       <c r="F8" t="n">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="G8" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價100</t>
+          <t>🟡 賠率1.67 考慮減碼</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,44 +466,79 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>建議停損(財報)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>建議主錨</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PE法停損</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PBR法停損</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>殖利率法停損</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>停損校準建議</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>①證偽</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>②估值過熱</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>③賠率</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>④拐點逆轉</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>⑤部位</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>⑥反向測試</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>⑦動態惡化</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -512,45 +547,68 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>118.5</v>
+        <v>226</v>
       </c>
       <c r="E2" t="n">
-        <v>117.63</v>
+        <v>236.26</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>🟠 賠率0.62&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="H2" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PE法</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>292</v>
+      </c>
+      <c r="L2" t="n">
+        <v>232.2</v>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>🟠 賠率0.92&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -559,31 +617,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>99.5</v>
+        <v>119.5</v>
       </c>
       <c r="E3" t="n">
-        <v>111.6</v>
+        <v>117.63</v>
       </c>
       <c r="F3" t="n">
         <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>🔴 跌破停損價100(現價99.5)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="H3" t="n">
+        <v>102</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PE法</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>102</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>105.9</v>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>✅ 手填停損與財報支撐一致</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,7 +687,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -613,116 +698,193 @@
       <c r="G4" t="n">
         <v>41</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PBR法</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>36</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>36</v>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>🟠 賠率0.67&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>225</v>
+        <v>660</v>
       </c>
       <c r="E5" t="n">
-        <v>236.26</v>
+        <v>636</v>
       </c>
       <c r="F5" t="n">
-        <v>250</v>
+        <v>720</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>🟡 賠率1.00 考慮減碼</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>540</v>
+      </c>
+      <c r="H5" t="n">
+        <v>569.4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PE法</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>569.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>526.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>559.2</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>🟠 賠率0.50&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>150</v>
+        <v>330.5</v>
       </c>
       <c r="E6" t="n">
-        <v>160.86</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>🟢 賠率2.33 持有</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>244.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PBR法</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>244.6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>🔴 賠率0.31&lt;0.5 立刻賣</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -731,41 +893,64 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>190.5</v>
       </c>
       <c r="E7" t="n">
-        <v>636</v>
+        <v>190.02</v>
       </c>
       <c r="F7" t="n">
-        <v>850</v>
+        <v>220</v>
       </c>
       <c r="G7" t="n">
-        <v>540</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>🟡 賠率1.63 考慮減碼</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>165</v>
+      </c>
+      <c r="H7" t="n">
+        <v>194</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PE法</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>194</v>
+      </c>
+      <c r="K7" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>235.2</v>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>🟡 賠率1.16 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
           <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -774,70 +959,120 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>315</v>
+        <v>98.2</v>
       </c>
       <c r="E8" t="n">
-        <v>305.63</v>
+        <v>111.6</v>
       </c>
       <c r="F8" t="n">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>🟡 賠率1.67 考慮減碼</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="H8" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PBR法</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="L8" t="n">
+        <v>100.4</v>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
+          <t>✅ 手填停損與財報支撐一致</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>🟡 賠率1.43 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>190</v>
+        <v>145.5</v>
       </c>
       <c r="E9" t="n">
-        <v>190.02</v>
+        <v>160.86</v>
       </c>
       <c r="F9" t="n">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>165</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>🟢 賠率2.32 持有</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>139</v>
+      </c>
+      <c r="H9" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PE法</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>113</v>
+      </c>
+      <c r="L9" t="n">
+        <v>123</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>✅ 手填停損與財報支撐一致</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>🟢 賠率11.46 持有</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -533,12 +533,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>226</v>
+        <v>119.5</v>
       </c>
       <c r="E2" t="n">
-        <v>236.26</v>
+        <v>117.63</v>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="H2" t="n">
-        <v>252.6</v>
+        <v>102</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -567,48 +567,48 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>252.6</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>292</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>232.2</v>
+        <v>105.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.92&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,55 +617,51 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>119.5</v>
+        <v>43.2</v>
       </c>
       <c r="E3" t="n">
-        <v>117.63</v>
+        <v>43.99</v>
       </c>
       <c r="F3" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="H3" t="n">
-        <v>102</v>
+        <v>34.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>87.59999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="L3" t="n">
-        <v>105.9</v>
+        <v>36</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
-        </is>
-      </c>
+          <t>🟠 賠率0.82&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -673,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -687,51 +683,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.4</v>
+        <v>137</v>
       </c>
       <c r="E4" t="n">
-        <v>43.99</v>
+        <v>160.86</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H4" t="n">
-        <v>34.9</v>
+        <v>138.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>138.9</v>
       </c>
       <c r="K4" t="n">
-        <v>34.9</v>
+        <v>113</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.67&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>🔴 跌破停損價139(現價137.0)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟠 賠率0.50&lt;1 應出場</t>
+          <t>🟠 賠率0.88&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -809,33 +809,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>330.5</v>
+        <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>111.6</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>76</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -843,48 +843,44 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>100.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.31&lt;0.5 立刻賣</t>
+          <t>🟡 賠率1.70 考慮減碼</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -893,19 +889,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>190.5</v>
+        <v>223</v>
       </c>
       <c r="E7" t="n">
-        <v>190.02</v>
+        <v>236.26</v>
       </c>
       <c r="F7" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="G7" t="n">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>194</v>
+        <v>252.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -913,44 +909,48 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>194</v>
+        <v>252.6</v>
       </c>
       <c r="K7" t="n">
-        <v>158.8</v>
+        <v>292</v>
       </c>
       <c r="L7" t="n">
-        <v>235.2</v>
+        <v>232.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.16 考慮減碼</t>
+          <t>🟡 賠率1.17 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,44 +959,44 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98.2</v>
+        <v>190</v>
       </c>
       <c r="E8" t="n">
-        <v>111.6</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>76</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>76.59999999999999</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>92.40000000000001</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>76.59999999999999</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>100.4</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.43 考慮減碼</t>
+          <t>🟡 賠率1.20 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1025,54 +1025,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>145.5</v>
+        <v>311</v>
       </c>
       <c r="E9" t="n">
-        <v>160.86</v>
+        <v>305.63</v>
       </c>
       <c r="F9" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>300</v>
       </c>
       <c r="H9" t="n">
-        <v>138.9</v>
+        <v>244.6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138.9</v>
+        <v>166.7</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>244.6</v>
       </c>
       <c r="L9" t="n">
-        <v>123</v>
+        <v>145.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率11.46 持有</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
-        </is>
-      </c>
+          <t>🟢 賠率2.64 持有</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級)</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -603,12 +603,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,54 +617,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43.2</v>
+        <v>638</v>
       </c>
       <c r="E3" t="n">
-        <v>43.99</v>
+        <v>636</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>720</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>540</v>
       </c>
       <c r="H3" t="n">
-        <v>34.9</v>
+        <v>569.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>36</v>
+        <v>569.4</v>
       </c>
       <c r="K3" t="n">
-        <v>34.9</v>
+        <v>526.2</v>
       </c>
       <c r="L3" t="n">
-        <v>36</v>
+        <v>559.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.82&lt;1 應出場</t>
+          <t>🟠 賠率0.84&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -683,7 +687,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E4" t="n">
         <v>160.86</v>
@@ -720,7 +724,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價137.0)</t>
+          <t>🔴 跌破停損價139(現價138.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -739,33 +743,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>636</v>
+        <v>189</v>
       </c>
       <c r="E5" t="n">
-        <v>636</v>
+        <v>190.02</v>
       </c>
       <c r="F5" t="n">
-        <v>720</v>
+        <v>220</v>
       </c>
       <c r="G5" t="n">
-        <v>540</v>
+        <v>165</v>
       </c>
       <c r="H5" t="n">
-        <v>569.4</v>
+        <v>194</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -773,24 +777,24 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>569.4</v>
+        <v>194</v>
       </c>
       <c r="K5" t="n">
-        <v>526.2</v>
+        <v>158.8</v>
       </c>
       <c r="L5" t="n">
-        <v>559.2</v>
+        <v>235.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟠 賠率0.88&lt;1 應出場</t>
+          <t>🟡 賠率1.29 考慮減碼</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -800,11 +804,7 @@
           <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>96</v>
+        <v>98.5</v>
       </c>
       <c r="E6" t="n">
         <v>111.6</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.70 考慮減碼</t>
+          <t>🟡 賠率1.40 考慮減碼</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.17 考慮減碼</t>
+          <t>🟡 賠率1.08 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,51 +959,51 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>190</v>
+        <v>42.7</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>43.99</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>34.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.20 考慮減碼</t>
+          <t>🟡 賠率1.35 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E9" t="n">
         <v>305.63</v>
@@ -1062,14 +1062,14 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.64 持有</t>
+          <t>🟡 賠率1.35 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>119.5</v>
+        <v>120.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🟠 賠率0.51&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -603,12 +603,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,68 +617,68 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>638</v>
+        <v>332</v>
       </c>
       <c r="E3" t="n">
-        <v>636</v>
+        <v>305.63</v>
       </c>
       <c r="F3" t="n">
-        <v>720</v>
+        <v>340</v>
       </c>
       <c r="G3" t="n">
-        <v>540</v>
+        <v>300</v>
       </c>
       <c r="H3" t="n">
-        <v>569.4</v>
+        <v>244.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>569.4</v>
+        <v>166.7</v>
       </c>
       <c r="K3" t="n">
-        <v>526.2</v>
+        <v>244.6</v>
       </c>
       <c r="L3" t="n">
-        <v>559.2</v>
+        <v>145.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.84&lt;1 應出場</t>
+          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -687,55 +687,51 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>138</v>
+        <v>43.4</v>
       </c>
       <c r="E4" t="n">
-        <v>160.86</v>
+        <v>43.99</v>
       </c>
       <c r="F4" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>138.9</v>
+        <v>34.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>138.9</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>113</v>
+        <v>34.9</v>
       </c>
       <c r="L4" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價138.0)</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
-        </is>
-      </c>
+          <t>🟠 賠率0.67&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -743,33 +739,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>189</v>
+        <v>667</v>
       </c>
       <c r="E5" t="n">
-        <v>190.02</v>
+        <v>636</v>
       </c>
       <c r="F5" t="n">
-        <v>220</v>
+        <v>720</v>
       </c>
       <c r="G5" t="n">
-        <v>165</v>
+        <v>540</v>
       </c>
       <c r="H5" t="n">
-        <v>194</v>
+        <v>569.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -777,24 +773,24 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>194</v>
+        <v>569.4</v>
       </c>
       <c r="K5" t="n">
-        <v>158.8</v>
+        <v>526.2</v>
       </c>
       <c r="L5" t="n">
-        <v>235.2</v>
+        <v>559.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.29 考慮減碼</t>
+          <t>🔴 賠率0.42&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -804,7 +800,11 @@
           <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>98.5</v>
+        <v>101</v>
       </c>
       <c r="E6" t="n">
         <v>111.6</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.40 考慮減碼</t>
+          <t>🟡 賠率1.16 考慮減碼</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.08 考慮減碼</t>
+          <t>🟡 賠率1.17 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,51 +959,51 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.7</v>
+        <v>187.5</v>
       </c>
       <c r="E8" t="n">
-        <v>43.99</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>34.9</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>34.9</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.35 考慮減碼</t>
+          <t>🟡 賠率1.44 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1011,12 +1011,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1025,58 +1025,54 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>142</v>
       </c>
       <c r="E9" t="n">
-        <v>305.63</v>
+        <v>160.86</v>
       </c>
       <c r="F9" t="n">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>300</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>244.6</v>
+        <v>138.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>166.7</v>
+        <v>138.9</v>
       </c>
       <c r="K9" t="n">
-        <v>244.6</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>145.3</v>
+        <v>123</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.35 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>🟢 賠率26.00 持有</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>120.5</v>
+        <v>121</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.51&lt;1 應出場</t>
+          <t>🔴 賠率0.47&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -603,12 +603,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>332</v>
+        <v>106.5</v>
       </c>
       <c r="E3" t="n">
-        <v>305.63</v>
+        <v>111.6</v>
       </c>
       <c r="F3" t="n">
-        <v>340</v>
+        <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>300</v>
+        <v>76</v>
       </c>
       <c r="H3" t="n">
-        <v>244.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -637,38 +637,34 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>166.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>244.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>145.3</v>
+        <v>100.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.77&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -753,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.42&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -809,33 +805,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>101</v>
+        <v>339</v>
       </c>
       <c r="E6" t="n">
-        <v>111.6</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>76</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>76.59999999999999</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -843,34 +839,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>92.40000000000001</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>76.59999999999999</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>100.4</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.16 考慮減碼</t>
+          <t>🔴 賠率0.03&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223</v>
+        <v>223.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.17 考慮減碼</t>
+          <t>🟡 賠率1.13 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>187.5</v>
+        <v>188.5</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.44 考慮減碼</t>
+          <t>🟡 賠率1.34 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率26.00 持有</t>
+          <t>🟢 賠率10.57 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -533,12 +533,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>228.5</v>
       </c>
       <c r="E2" t="n">
-        <v>117.63</v>
+        <v>236.26</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>102</v>
+        <v>252.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -567,48 +567,48 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>102</v>
+        <v>252.6</v>
       </c>
       <c r="K2" t="n">
-        <v>87.59999999999999</v>
+        <v>292</v>
       </c>
       <c r="L2" t="n">
-        <v>105.9</v>
+        <v>232.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.47&lt;0.5 立刻賣</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
-        </is>
-      </c>
+          <t>🟠 賠率0.75&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,33 +617,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>106.5</v>
+        <v>121.5</v>
       </c>
       <c r="E3" t="n">
-        <v>111.6</v>
+        <v>117.63</v>
       </c>
       <c r="F3" t="n">
         <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="H3" t="n">
-        <v>76.59999999999999</v>
+        <v>102</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>92.40000000000001</v>
+        <v>102</v>
       </c>
       <c r="K3" t="n">
-        <v>76.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>100.4</v>
+        <v>105.9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -654,10 +654,14 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.77&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -683,7 +687,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +724,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.67&lt;1 應出場</t>
+          <t>🟠 賠率0.90&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>682</v>
+        <v>699</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.13&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>339</v>
+        <v>327.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.03&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.45&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -875,12 +879,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -889,68 +893,64 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223.5</v>
+        <v>102.5</v>
       </c>
       <c r="E7" t="n">
-        <v>236.26</v>
+        <v>111.6</v>
       </c>
       <c r="F7" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="H7" t="n">
-        <v>252.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>252.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>292</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>232.2</v>
+        <v>100.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.13 考慮減碼</t>
+          <t>🟡 賠率1.04 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>188.5</v>
+        <v>148</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>160.86</v>
       </c>
       <c r="F8" t="n">
         <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -979,65 +979,65 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>113</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>123</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.34 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>🟢 賠率8.00 持有</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟢 抱緊</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>146</v>
+        <v>181.5</v>
       </c>
       <c r="E9" t="n">
-        <v>160.86</v>
+        <v>190.02</v>
       </c>
       <c r="F9" t="n">
         <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="H9" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1045,31 +1045,27 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>158.8</v>
       </c>
       <c r="L9" t="n">
-        <v>123</v>
+        <v>235.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率10.57 持有</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
-        </is>
-      </c>
+          <t>🟢 賠率2.33 持有</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>228.5</v>
+        <v>231</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.75&lt;1 應出場</t>
+          <t>🟠 賠率0.61&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -603,12 +603,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,33 +617,33 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>121.5</v>
+        <v>107</v>
       </c>
       <c r="E3" t="n">
-        <v>117.63</v>
+        <v>111.6</v>
       </c>
       <c r="F3" t="n">
         <v>130</v>
       </c>
       <c r="G3" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="H3" t="n">
-        <v>102</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>102</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>87.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>105.9</v>
+        <v>100.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -654,14 +654,10 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
-        </is>
-      </c>
+          <t>🟠 賠率0.74&lt;1 應出場</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
@@ -673,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -687,51 +683,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.1</v>
+        <v>123.5</v>
       </c>
       <c r="E4" t="n">
-        <v>43.99</v>
+        <v>117.63</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="H4" t="n">
-        <v>34.9</v>
+        <v>102</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="K4" t="n">
-        <v>34.9</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>105.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.90&lt;1 應出場</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>🔴 賠率0.30&lt;0.5 立刻賣</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>699</v>
+        <v>721</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.13&lt;0.5 立刻賣</t>
+          <t>🔴 賠率-0.01&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>327.5</v>
+        <v>334</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.45&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.18&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -879,33 +879,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>102.5</v>
+        <v>43.3</v>
       </c>
       <c r="E7" t="n">
-        <v>111.6</v>
+        <v>43.99</v>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>76.59999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>92.40000000000001</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>76.59999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="L7" t="n">
-        <v>100.4</v>
+        <v>36</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.04 考慮減碼</t>
+          <t>🟠 賠率0.74&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E8" t="n">
         <v>160.86</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率8.00 持有</t>
+          <t>🟢 賠率7.10 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>181.5</v>
+        <v>182.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.33 持有</t>
+          <t>🟢 賠率2.14 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.61&lt;1 應出場</t>
+          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.74&lt;1 應出場</t>
+          <t>🟠 賠率0.59&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>123.5</v>
+        <v>122.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.30&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率-0.01&lt;0.5 立刻賣</t>
+          <t>🔴 賠率-0.09&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.18&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>149</v>
+        <v>148.5</v>
       </c>
       <c r="E8" t="n">
         <v>160.86</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率7.10 持有</t>
+          <t>🟢 賠率7.53 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>182.5</v>
+        <v>180.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.14 持有</t>
+          <t>🟢 賠率2.55 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.59&lt;1 應出場</t>
+          <t>🟠 賠率0.74&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率-0.09&lt;0.5 立刻賣</t>
+          <t>🔴 賠率-0.03&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
+          <t>🔴 賠率-0.23&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -930,7 +930,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟠 賠率0.74&lt;1 應出場</t>
+          <t>🟠 賠率0.67&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>148.5</v>
+        <v>144</v>
       </c>
       <c r="E8" t="n">
         <v>160.86</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率7.53 持有</t>
+          <t>🟢 賠率15.20 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>180.5</v>
+        <v>178.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.55 持有</t>
+          <t>🟢 賠率3.07 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>107</v>
+        <v>107.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.74&lt;1 應出場</t>
+          <t>🟠 賠率0.71&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率-0.03&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.02&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -930,7 +930,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟠 賠率0.67&lt;1 應出場</t>
+          <t>🟠 賠率0.90&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,33 +945,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟢 抱緊</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="E8" t="n">
-        <v>160.86</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
         <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -979,31 +979,27 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>113</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>123</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率15.20 持有</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(22.5→15.0→14.9)</t>
-        </is>
-      </c>
+          <t>🟢 賠率2.93 持有</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -1011,12 +1007,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1025,19 +1021,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>178.5</v>
+        <v>143.5</v>
       </c>
       <c r="E9" t="n">
-        <v>190.02</v>
+        <v>160.86</v>
       </c>
       <c r="F9" t="n">
         <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1045,24 +1041,24 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="K9" t="n">
-        <v>158.8</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>235.2</v>
+        <v>123</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.07 持有</t>
+          <t>🟢 賠率17.00 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
+          <t>🔴 賠率-0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>107.5</v>
+        <v>43.6</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.71&lt;1 應出場</t>
+          <t>🔴 跌破停損價76(現價43.6)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,14 +720,10 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(9.3→4.3→0.6)</t>
-        </is>
-      </c>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
@@ -753,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.02&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.00&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -809,12 +805,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -823,19 +819,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>352</v>
+        <v>32.3</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -843,24 +839,24 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率-0.23&lt;0.5 立刻賣</t>
+          <t>🔴 跌破停損價41(現價32.3)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -870,21 +866,17 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -893,51 +885,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43.1</v>
+        <v>53.2</v>
       </c>
       <c r="E7" t="n">
-        <v>43.99</v>
+        <v>160.86</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H7" t="n">
-        <v>34.9</v>
+        <v>138.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36</v>
+        <v>138.9</v>
       </c>
       <c r="K7" t="n">
-        <v>34.9</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟠 賠率0.90&lt;1 應出場</t>
+          <t>🔴 跌破停損價139(現價53.2)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -945,74 +937,82 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179</v>
+        <v>79.5</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>305.63</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>244.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>166.7</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>244.6</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>145.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.93 持有</t>
+          <t>🔴 跌破停損價300(現價79.5)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1021,19 +1021,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>143.5</v>
+        <v>176</v>
       </c>
       <c r="E9" t="n">
-        <v>160.86</v>
+        <v>190.02</v>
       </c>
       <c r="F9" t="n">
         <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="H9" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1041,24 +1041,24 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>158.8</v>
       </c>
       <c r="L9" t="n">
-        <v>123</v>
+        <v>235.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率17.00 持有</t>
+          <t>🟢 賠率4.00 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率-0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43.6</v>
+        <v>112</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價76(現價43.6)</t>
+          <t>🟠 賠率0.50&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -805,12 +805,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.3</v>
+        <v>363</v>
       </c>
       <c r="E6" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價41(現價32.3)</t>
+          <t>🔴 賠率-0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -866,17 +866,21 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -885,51 +889,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53.2</v>
+        <v>43.8</v>
       </c>
       <c r="E7" t="n">
-        <v>160.86</v>
+        <v>43.99</v>
       </c>
       <c r="F7" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>138.9</v>
+        <v>34.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>138.9</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>113</v>
+        <v>34.9</v>
       </c>
       <c r="L7" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價53.2)</t>
+          <t>🔴 賠率0.43&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -937,82 +941,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟢 抱緊</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>79.5</v>
+        <v>176</v>
       </c>
       <c r="E8" t="n">
-        <v>305.63</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>244.6</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>166.7</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>244.6</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>145.3</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價79.5)</t>
+          <t>🟢 賠率4.00 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1021,19 +1017,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>142.5</v>
       </c>
       <c r="E9" t="n">
-        <v>190.02</v>
+        <v>160.86</v>
       </c>
       <c r="F9" t="n">
         <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1041,24 +1037,24 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="K9" t="n">
-        <v>158.8</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>235.2</v>
+        <v>123</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率4.00 持有</t>
+          <t>🟢 賠率22.14 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>241</v>
+        <v>239.5</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.50&lt;1 應出場</t>
+          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>720</v>
+        <v>669</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.00&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -805,12 +805,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>363</v>
+        <v>43.5</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率-0.37&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -866,21 +866,17 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -889,51 +885,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43.8</v>
+        <v>138</v>
       </c>
       <c r="E7" t="n">
-        <v>43.99</v>
+        <v>160.86</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H7" t="n">
-        <v>34.9</v>
+        <v>138.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36</v>
+        <v>138.9</v>
       </c>
       <c r="K7" t="n">
-        <v>34.9</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 賠率0.43&lt;0.5 立刻賣</t>
+          <t>🔴 跌破停損價139(現價138.0)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -941,74 +937,82 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>176</v>
+        <v>327</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>305.63</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>244.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>166.7</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>244.6</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>145.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率4.00 持有</t>
+          <t>🔴 賠率0.48&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1017,19 +1021,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>142.5</v>
+        <v>177</v>
       </c>
       <c r="E9" t="n">
-        <v>160.86</v>
+        <v>190.02</v>
       </c>
       <c r="F9" t="n">
         <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="H9" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1037,24 +1041,24 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>158.8</v>
       </c>
       <c r="L9" t="n">
-        <v>123</v>
+        <v>235.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率22.14 持有</t>
+          <t>🟢 賠率3.58 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>239.5</v>
+        <v>242</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.19&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>114.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.55&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
         <v>43.99</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>138</v>
+        <v>133.5</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價138.0)</t>
+          <t>🔴 跌破停損價139(現價133.5)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -947,11 +947,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>309.5</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -988,14 +988,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 賠率0.48&lt;0.5 立刻賣</t>
+          <t>🟢 賠率3.21 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>175.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.58 持有</t>
+          <t>🟢 賠率4.24 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>242</v>
+        <v>244.5</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.19&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.12&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>114.5</v>
+        <v>115.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟠 賠率0.55&lt;1 應出場</t>
+          <t>🔴 賠率0.31&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="E6" t="n">
         <v>43.99</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.29&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>133.5</v>
+        <v>139</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價133.5)</t>
+          <t>🔴 跌破停損價139(現價139.0)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>309.5</v>
+        <v>302</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率3.21 持有</t>
+          <t>🟢 賠率19.00 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率4.24 持有</t>
+          <t>🟢 賠率3.58 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>244.5</v>
+        <v>245.5</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.12&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.10&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115.5</v>
+        <v>113.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>122.5</v>
+        <v>122</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -735,12 +735,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>677</v>
+        <v>135</v>
       </c>
       <c r="E5" t="n">
-        <v>636</v>
+        <v>160.86</v>
       </c>
       <c r="F5" t="n">
-        <v>720</v>
+        <v>220</v>
       </c>
       <c r="G5" t="n">
-        <v>540</v>
+        <v>139</v>
       </c>
       <c r="H5" t="n">
-        <v>569.4</v>
+        <v>138.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -769,24 +769,24 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>569.4</v>
+        <v>138.9</v>
       </c>
       <c r="K5" t="n">
-        <v>526.2</v>
+        <v>113</v>
       </c>
       <c r="L5" t="n">
-        <v>559.2</v>
+        <v>123</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.31&lt;0.5 立刻賣</t>
+          <t>🔴 跌破停損價139(現價135.0)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -796,21 +796,17 @@
           <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
-        </is>
-      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,19 +815,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44.1</v>
+        <v>295</v>
       </c>
       <c r="E6" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -839,24 +835,24 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.29&lt;0.5 立刻賣</t>
+          <t>🔴 跌破停損價300(現價295.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -866,17 +862,21 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -885,51 +885,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>160.86</v>
+        <v>43.99</v>
       </c>
       <c r="F7" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>138.9</v>
+        <v>34.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>138.9</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>113</v>
+        <v>34.9</v>
       </c>
       <c r="L7" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價139.0)</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -937,12 +937,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -951,56 +951,56 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>623</v>
       </c>
       <c r="E8" t="n">
-        <v>305.63</v>
+        <v>636</v>
       </c>
       <c r="F8" t="n">
-        <v>340</v>
+        <v>720</v>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
+        <v>540</v>
       </c>
       <c r="H8" t="n">
-        <v>244.6</v>
+        <v>569.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>166.7</v>
+        <v>569.4</v>
       </c>
       <c r="K8" t="n">
-        <v>244.6</v>
+        <v>526.2</v>
       </c>
       <c r="L8" t="n">
-        <v>145.3</v>
+        <v>559.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率19.00 持有</t>
+          <t>🟡 賠率1.17 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>178.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.58 持有</t>
+          <t>🟢 賠率3.07 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>245.5</v>
+        <v>243</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.10&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.16&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>113.5</v>
+        <v>110</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.59&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E5" t="n">
         <v>160.86</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價135.0)</t>
+          <t>🔴 跌破停損價139(現價127.0)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -852,7 +852,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價295.0)</t>
+          <t>🔴 跌破停損價300(現價286.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E8" t="n">
         <v>636</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.17 考慮減碼</t>
+          <t>🟡 賠率1.40 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>178.5</v>
+        <v>175</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.07 持有</t>
+          <t>🟢 賠率4.50 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>243</v>
+        <v>243.5</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.16&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.15&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>110</v>
+        <v>109.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.59&lt;1 應出場</t>
+          <t>🟠 賠率0.61&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>127</v>
+        <v>125.5</v>
       </c>
       <c r="E5" t="n">
         <v>160.86</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價127.0)</t>
+          <t>🔴 跌破停損價139(現價125.5)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -852,7 +852,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價286.0)</t>
+          <t>🔴 跌破停損價300(現價274.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44.2</v>
+        <v>43.8</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 賠率0.25&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.43&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="E8" t="n">
         <v>636</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.40 考慮減碼</t>
+          <t>🟡 賠率1.54 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>175.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率4.50 持有</t>
+          <t>🟢 賠率4.24 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>243.5</v>
+        <v>243</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.15&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.16&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>109.5</v>
+        <v>116.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.61&lt;1 應出場</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -735,12 +735,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>125.5</v>
+        <v>633</v>
       </c>
       <c r="E5" t="n">
-        <v>160.86</v>
+        <v>636</v>
       </c>
       <c r="F5" t="n">
-        <v>220</v>
+        <v>720</v>
       </c>
       <c r="G5" t="n">
-        <v>139</v>
+        <v>540</v>
       </c>
       <c r="H5" t="n">
-        <v>138.9</v>
+        <v>569.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -769,24 +769,24 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>138.9</v>
+        <v>569.4</v>
       </c>
       <c r="K5" t="n">
-        <v>113</v>
+        <v>526.2</v>
       </c>
       <c r="L5" t="n">
-        <v>123</v>
+        <v>559.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價125.5)</t>
+          <t>🟠 賠率0.94&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -796,17 +796,21 @@
           <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -815,19 +819,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>274</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -835,24 +839,24 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價274.0)</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -862,21 +866,17 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -885,51 +885,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>43.8</v>
+        <v>128.5</v>
       </c>
       <c r="E7" t="n">
-        <v>43.99</v>
+        <v>160.86</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H7" t="n">
-        <v>34.9</v>
+        <v>138.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36</v>
+        <v>138.9</v>
       </c>
       <c r="K7" t="n">
-        <v>34.9</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 賠率0.43&lt;0.5 立刻賣</t>
+          <t>🔴 跌破停損價139(現價128.5)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -937,70 +937,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>611</v>
+        <v>288</v>
       </c>
       <c r="E8" t="n">
-        <v>636</v>
+        <v>305.63</v>
       </c>
       <c r="F8" t="n">
-        <v>720</v>
+        <v>340</v>
       </c>
       <c r="G8" t="n">
-        <v>540</v>
+        <v>300</v>
       </c>
       <c r="H8" t="n">
-        <v>569.4</v>
+        <v>244.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>569.4</v>
+        <v>166.7</v>
       </c>
       <c r="K8" t="n">
-        <v>526.2</v>
+        <v>244.6</v>
       </c>
       <c r="L8" t="n">
-        <v>559.2</v>
+        <v>145.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.54 考慮減碼</t>
+          <t>🔴 跌破停損價300(現價288.0)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>175.5</v>
+        <v>179</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率4.24 持有</t>
+          <t>🟢 賠率2.93 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>243</v>
+        <v>239.5</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.16&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116.5</v>
+        <v>114.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.47&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟠 賠率0.94&lt;1 應出場</t>
+          <t>🟠 賠率0.98&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="E6" t="n">
         <v>43.99</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>128.5</v>
+        <v>132</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價128.5)</t>
+          <t>🔴 跌破停損價139(現價132.0)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>299.5</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價288.0)</t>
+          <t>🔴 跌破停損價300(現價299.5)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>176.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.93 持有</t>
+          <t>🟢 賠率3.78 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>239.5</v>
+        <v>237</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>114.5</v>
+        <v>113.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.47&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.56&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟠 賠率0.98&lt;1 應出場</t>
+          <t>🟠 賠率0.89&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>132</v>
+        <v>133.5</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價132.0)</t>
+          <t>🔴 跌破停損價139(現價133.5)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>299.5</v>
+        <v>298</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價299.5)</t>
+          <t>🔴 跌破停損價300(現價298.0)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>176.5</v>
+        <v>176</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.78 持有</t>
+          <t>🟢 賠率4.00 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>113.5</v>
+        <v>113</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.46&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>635</v>
+        <v>651</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟠 賠率0.89&lt;1 應出場</t>
+          <t>🟠 賠率0.62&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="E6" t="n">
         <v>43.99</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🟠 賠率0.67&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>133.5</v>
+        <v>130</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價133.5)</t>
+          <t>🔴 跌破停損價139(現價130.0)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價298.0)</t>
+          <t>🔴 跌破停損價300(現價294.0)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>178.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率4.00 持有</t>
+          <t>🟢 賠率3.07 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>241</v>
+        <v>239.5</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>112.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.46&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.48&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.56&lt;1 應出場</t>
+          <t>🟠 賠率0.51&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>651</v>
+        <v>668</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟠 賠率0.62&lt;1 應出場</t>
+          <t>🔴 賠率0.41&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="E6" t="n">
         <v>43.99</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟠 賠率0.67&lt;1 應出場</t>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>130</v>
+        <v>131.5</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價130.0)</t>
+          <t>🔴 跌破停損價139(現價131.5)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>293.5</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價294.0)</t>
+          <t>🔴 跌破停損價300(現價293.5)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>178.5</v>
+        <v>177.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.07 持有</t>
+          <t>🟢 賠率3.40 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>239.5</v>
+        <v>237.5</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>112.5</v>
+        <v>110</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.48&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.59&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120.5</v>
+        <v>120</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.51&lt;1 應出場</t>
+          <t>🟠 賠率0.56&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.41&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.29&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>131.5</v>
+        <v>126.5</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價131.5)</t>
+          <t>🔴 跌破停損價139(現價126.5)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>293.5</v>
+        <v>273.5</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -988,7 +988,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價293.5)</t>
+          <t>🔴 跌破停損價300(現價273.5)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>177.5</v>
+        <v>177</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.40 持有</t>
+          <t>🟢 賠率3.58 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>237.5</v>
+        <v>241</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.59&lt;1 應出場</t>
+          <t>🟠 賠率0.74&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120</v>
+        <v>120.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.56&lt;1 應出場</t>
+          <t>🟠 賠率0.51&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>679</v>
+        <v>720</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.29&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.00&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -805,12 +805,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43.5</v>
+        <v>264.5</v>
       </c>
       <c r="E6" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🔴 跌破停損價300(現價264.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -866,7 +866,11 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -885,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>126.5</v>
+        <v>124.5</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -922,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價126.5)</t>
+          <t>🔴 跌破停損價139(現價124.5)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -937,33 +941,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>273.5</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F8" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -971,24 +975,24 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價273.5)</t>
+          <t>🟡 賠率1.00 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -998,11 +1002,7 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.58 持有</t>
+          <t>🟢 賠率4.00 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E2" t="n">
         <v>236.26</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.22&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.67&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.74&lt;1 應出場</t>
+          <t>🟠 賠率0.59&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>120.5</v>
+        <v>121.5</v>
       </c>
       <c r="E4" t="n">
         <v>117.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.51&lt;1 應出場</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>264.5</v>
+        <v>254.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價264.5)</t>
+          <t>🔴 跌破停損價300(現價254.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>124.5</v>
+        <v>120.5</v>
       </c>
       <c r="E7" t="n">
         <v>160.86</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價124.5)</t>
+          <t>🔴 跌破停損價139(現價120.5)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -951,11 +951,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 警戒</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42.3</v>
       </c>
       <c r="E8" t="n">
         <v>43.99</v>
@@ -992,14 +992,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.00 考慮減碼</t>
+          <t>🟢 賠率2.08 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率4.00 持有</t>
+          <t>🟢 賠率2.93 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -533,12 +533,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,19 +547,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>236.26</v>
+        <v>117.63</v>
       </c>
       <c r="F2" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="G2" t="n">
-        <v>200</v>
+        <v>102</v>
       </c>
       <c r="H2" t="n">
-        <v>252.6</v>
+        <v>102</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -567,38 +567,34 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>252.6</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>292</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>232.2</v>
+        <v>105.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🟠 賠率0.67&lt;1 應出場</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -617,7 +613,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +650,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🟠 賠率0.59&lt;1 應出場</t>
+          <t>🔴 賠率0.42&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +665,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +679,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>121.5</v>
+        <v>131</v>
       </c>
       <c r="E4" t="n">
-        <v>117.63</v>
+        <v>160.86</v>
       </c>
       <c r="F4" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="G4" t="n">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="H4" t="n">
-        <v>102</v>
+        <v>138.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,13 +699,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>102</v>
+        <v>138.9</v>
       </c>
       <c r="K4" t="n">
-        <v>87.59999999999999</v>
+        <v>113</v>
       </c>
       <c r="L4" t="n">
-        <v>105.9</v>
+        <v>123</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -720,7 +716,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🔴 跌破停損價139(現價131.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -819,7 +815,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>254.5</v>
+        <v>266.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +852,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價254.5)</t>
+          <t>🔴 跌破停損價300(現價266.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -875,33 +871,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>120.5</v>
+        <v>224</v>
       </c>
       <c r="E7" t="n">
-        <v>160.86</v>
+        <v>236.26</v>
       </c>
       <c r="F7" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="G7" t="n">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>138.9</v>
+        <v>252.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -909,34 +905,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>138.9</v>
+        <v>252.6</v>
       </c>
       <c r="K7" t="n">
-        <v>113</v>
+        <v>292</v>
       </c>
       <c r="L7" t="n">
-        <v>123</v>
+        <v>232.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價120.5)</t>
+          <t>🟡 賠率1.08 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -951,11 +951,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟡 警戒</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="E8" t="n">
         <v>43.99</v>
@@ -992,14 +992,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.08 持有</t>
+          <t>🟡 賠率1.67 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>179</v>
+        <v>181.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.93 持有</t>
+          <t>🟢 賠率2.33 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>114</v>
+        <v>114.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -650,7 +650,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.42&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>131</v>
+        <v>136.5</v>
       </c>
       <c r="E4" t="n">
         <v>160.86</v>
@@ -716,7 +716,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價131.0)</t>
+          <t>🔴 跌破停損價139(現價136.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>266.5</v>
+        <v>276</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -852,7 +852,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價266.5)</t>
+          <t>🔴 跌破停損價300(現價276.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>224</v>
+        <v>220.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.08 考慮減碼</t>
+          <t>🟡 賠率1.44 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.5</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
         <v>43.99</v>
@@ -992,7 +992,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.67 考慮減碼</t>
+          <t>🟡 賠率1.00 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>181.5</v>
+        <v>179.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.33 持有</t>
+          <t>🟢 賠率2.79 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>124</v>
+        <v>122.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>114.5</v>
+        <v>114</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -650,7 +650,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.42&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>136.5</v>
+        <v>135.5</v>
       </c>
       <c r="E4" t="n">
         <v>160.86</v>
@@ -716,7 +716,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價136.5)</t>
+          <t>🔴 跌破停損價139(現價135.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -852,7 +852,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價276.0)</t>
+          <t>🔴 跌破停損價300(現價280.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>220.5</v>
+        <v>221.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -922,7 +922,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.44 考慮減碼</t>
+          <t>🟡 賠率1.33 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="E8" t="n">
         <v>43.99</v>
@@ -992,7 +992,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.00 考慮減碼</t>
+          <t>🟡 賠率1.22 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>179.5</v>
+        <v>178.5</v>
       </c>
       <c r="E9" t="n">
         <v>190.02</v>
@@ -1058,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.79 持有</t>
+          <t>🟢 賠率3.07 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -650,7 +650,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.42&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -665,12 +665,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -679,54 +679,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>135.5</v>
+        <v>292.5</v>
       </c>
       <c r="E4" t="n">
-        <v>160.86</v>
+        <v>305.63</v>
       </c>
       <c r="F4" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>139</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>138.9</v>
+        <v>244.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>138.9</v>
+        <v>166.7</v>
       </c>
       <c r="K4" t="n">
-        <v>113</v>
+        <v>244.6</v>
       </c>
       <c r="L4" t="n">
-        <v>123</v>
+        <v>145.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價139(現價135.5)</t>
+          <t>🔴 跌破停損價300(現價292.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -801,33 +805,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>280</v>
+        <v>42.6</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -835,24 +839,24 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價280.0)</t>
+          <t>🟡 賠率1.50 考慮減碼</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -862,11 +866,7 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -941,78 +941,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟢 抱緊</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.8</v>
+        <v>179</v>
       </c>
       <c r="E8" t="n">
-        <v>43.99</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>34.9</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>34.9</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.22 考慮減碼</t>
+          <t>🟢 賠率2.93 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1021,19 +1017,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>178.5</v>
+        <v>140.5</v>
       </c>
       <c r="E9" t="n">
-        <v>190.02</v>
+        <v>160.86</v>
       </c>
       <c r="F9" t="n">
         <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1041,24 +1037,24 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>194</v>
+        <v>138.9</v>
       </c>
       <c r="K9" t="n">
-        <v>158.8</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>235.2</v>
+        <v>123</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率3.07 持有</t>
+          <t>🟢 賠率53.00 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -650,7 +650,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -665,12 +665,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -679,89 +679,89 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.5</v>
+        <v>720</v>
       </c>
       <c r="E4" t="n">
-        <v>305.63</v>
+        <v>636</v>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>720</v>
       </c>
       <c r="G4" t="n">
-        <v>300</v>
+        <v>540</v>
       </c>
       <c r="H4" t="n">
-        <v>244.6</v>
+        <v>569.4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>166.7</v>
+        <v>569.4</v>
       </c>
       <c r="K4" t="n">
-        <v>244.6</v>
+        <v>526.2</v>
       </c>
       <c r="L4" t="n">
-        <v>145.3</v>
+        <v>559.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價292.5)</t>
+          <t>🔴 賠率0.00&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>720</v>
+        <v>220</v>
       </c>
       <c r="E5" t="n">
-        <v>636</v>
+        <v>236.26</v>
       </c>
       <c r="F5" t="n">
-        <v>720</v>
+        <v>250</v>
       </c>
       <c r="G5" t="n">
-        <v>540</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>569.4</v>
+        <v>252.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -769,48 +769,48 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>569.4</v>
+        <v>252.6</v>
       </c>
       <c r="K5" t="n">
-        <v>526.2</v>
+        <v>292</v>
       </c>
       <c r="L5" t="n">
-        <v>559.2</v>
+        <v>232.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 賠率0.00&lt;0.5 立刻賣</t>
+          <t>🟡 賠率1.50 考慮減碼</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>42.6</v>
+        <v>308.5</v>
       </c>
       <c r="E6" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -839,44 +839,48 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.50 考慮減碼</t>
+          <t>🟢 賠率3.71 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -885,44 +889,44 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>221.5</v>
+        <v>42.6</v>
       </c>
       <c r="E7" t="n">
-        <v>236.26</v>
+        <v>43.99</v>
       </c>
       <c r="F7" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>252.6</v>
+        <v>34.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>252.6</v>
+        <v>36</v>
       </c>
       <c r="K7" t="n">
-        <v>292</v>
+        <v>34.9</v>
       </c>
       <c r="L7" t="n">
-        <v>232.2</v>
+        <v>36</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.33 考慮減碼</t>
+          <t>🟡 賠率1.50 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -932,11 +936,7 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179</v>
+        <v>179.5</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -992,7 +992,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.93 持有</t>
+          <t>🟢 賠率2.79 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>140.5</v>
+        <v>154.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1054,7 +1054,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率53.00 持有</t>
+          <t>🟢 賠率4.23 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,10 +584,14 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>🟡 最新月YoY-15.4%轉負</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -613,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115.5</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -650,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -749,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E5" t="n">
         <v>236.26</v>
@@ -786,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.50 考慮減碼</t>
+          <t>🟡 賠率1.38 考慮減碼</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>308.5</v>
+        <v>310.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率3.71 持有</t>
+          <t>🟢 賠率2.81 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -926,7 +930,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.50 考慮減碼</t>
+          <t>🟡 賠率1.67 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -955,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179.5</v>
+        <v>181</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -992,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.79 持有</t>
+          <t>🟢 賠率2.44 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1017,7 +1021,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>154.5</v>
+        <v>151.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1054,7 +1058,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率4.23 持有</t>
+          <t>🟢 賠率5.48 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>114.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>720</v>
+        <v>79.2</v>
       </c>
       <c r="E4" t="n">
         <v>636</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 賠率0.00&lt;0.5 立刻賣</t>
+          <t>🔴 跌破停損價540(現價79.2)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>221</v>
+        <v>219.5</v>
       </c>
       <c r="E5" t="n">
         <v>236.26</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.38 考慮減碼</t>
+          <t>🟡 賠率1.56 考慮減碼</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -809,12 +809,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -823,58 +823,58 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>310.5</v>
+        <v>184.5</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>190.02</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>194</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>158.8</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>235.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.81 持有</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>🟡 賠率1.82 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -945,64 +945,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>181</v>
+        <v>311</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>305.63</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>244.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>166.7</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>244.6</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>145.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.44 持有</t>
+          <t>🟢 賠率2.64 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1021,7 +1029,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>151.5</v>
+        <v>149.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1058,7 +1066,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率5.48 持有</t>
+          <t>🟢 賠率6.71 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>121.5</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>636</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價79.2)</t>
+          <t>🔴 跌破停損價540(現價87.1)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>219.5</v>
+        <v>219</v>
       </c>
       <c r="E5" t="n">
         <v>236.26</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.56 考慮減碼</t>
+          <t>🟡 賠率1.63 考慮減碼</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>184.5</v>
+        <v>183</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.82 考慮減碼</t>
+          <t>🟢 賠率2.06 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -869,11 +869,7 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -893,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -930,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.67 考慮減碼</t>
+          <t>🟡 賠率1.50 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -996,7 +992,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.64 持有</t>
+          <t>🟢 賠率5.67 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1029,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>149.5</v>
+        <v>151.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1066,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率6.71 持有</t>
+          <t>🟢 賠率5.48 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>87.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="E4" t="n">
         <v>636</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價87.1)</t>
+          <t>🔴 跌破停損價540(現價82.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>219</v>
+        <v>219.5</v>
       </c>
       <c r="E5" t="n">
         <v>236.26</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.63 考慮減碼</t>
+          <t>🟡 賠率1.56 考慮減碼</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.50 考慮減碼</t>
+          <t>🟡 賠率1.22 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>306</v>
+        <v>311.5</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -992,7 +992,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率5.67 持有</t>
+          <t>🟢 賠率2.48 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>151.5</v>
+        <v>150.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率5.48 持有</t>
+          <t>🟢 賠率6.04 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82.5</v>
+        <v>81.8</v>
       </c>
       <c r="E4" t="n">
         <v>636</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價82.5)</t>
+          <t>🔴 跌破停損價540(現價81.8)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>219.5</v>
+        <v>217</v>
       </c>
       <c r="E5" t="n">
         <v>236.26</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.56 考慮減碼</t>
+          <t>🟡 賠率1.94 考慮減碼</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>183</v>
+        <v>182.5</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.06 持有</t>
+          <t>🟢 賠率2.14 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.22 考慮減碼</t>
+          <t>🟡 賠率1.67 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>311.5</v>
+        <v>315.5</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -992,14 +992,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.48 持有</t>
+          <t>🟡 賠率1.58 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>150.5</v>
+        <v>149.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率6.04 持有</t>
+          <t>🟢 賠率6.71 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>114.5</v>
+        <v>116.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81.8</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
         <v>636</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價81.8)</t>
+          <t>🔴 跌破停損價540(現價79.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>217</v>
+        <v>214.5</v>
       </c>
       <c r="E5" t="n">
         <v>236.26</v>
@@ -790,14 +790,14 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟡 賠率1.94 考慮減碼</t>
+          <t>🟢 賠率2.45 持有</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>315.5</v>
+        <v>306</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -992,14 +992,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.58 考慮減碼</t>
+          <t>🟢 賠率5.67 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>149.5</v>
+        <v>146</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率6.71 持有</t>
+          <t>🟢 賠率10.57 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116.5</v>
+        <v>121.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.19&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79</v>
+        <v>76.5</v>
       </c>
       <c r="E4" t="n">
         <v>636</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價79.0)</t>
+          <t>🔴 跌破停損價540(現價76.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>214.5</v>
+        <v>213</v>
       </c>
       <c r="E5" t="n">
         <v>236.26</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟢 賠率2.45 持有</t>
+          <t>🟢 賠率2.85 持有</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>182.5</v>
+        <v>183</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.14 持有</t>
+          <t>🟢 賠率2.06 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
       <c r="E7" t="n">
         <v>43.99</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.67 考慮減碼</t>
+          <t>🟡 賠率1.11 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E8" t="n">
         <v>305.63</v>
@@ -992,7 +992,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率5.67 持有</t>
+          <t>🟢 賠率12.33 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率10.57 持有</t>
+          <t>🟢 賠率8.00 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>121.5</v>
+        <v>117.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.19&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.30&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>寶雅</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,89 +683,89 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76.5</v>
+        <v>288</v>
       </c>
       <c r="E4" t="n">
-        <v>636</v>
+        <v>305.63</v>
       </c>
       <c r="F4" t="n">
-        <v>720</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>540</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>569.4</v>
+        <v>244.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>569.4</v>
+        <v>166.7</v>
       </c>
       <c r="K4" t="n">
-        <v>526.2</v>
+        <v>244.6</v>
       </c>
       <c r="L4" t="n">
-        <v>559.2</v>
+        <v>145.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價76.5)</t>
+          <t>🔴 跌破停損價300(現價288.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>寶雅</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>213</v>
+        <v>78.7</v>
       </c>
       <c r="E5" t="n">
-        <v>236.26</v>
+        <v>636</v>
       </c>
       <c r="F5" t="n">
-        <v>250</v>
+        <v>720</v>
       </c>
       <c r="G5" t="n">
-        <v>200</v>
+        <v>540</v>
       </c>
       <c r="H5" t="n">
-        <v>252.6</v>
+        <v>569.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -773,36 +773,36 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>252.6</v>
+        <v>569.4</v>
       </c>
       <c r="K5" t="n">
-        <v>292</v>
+        <v>526.2</v>
       </c>
       <c r="L5" t="n">
-        <v>232.2</v>
+        <v>559.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
+          <t>⚠️ 手填停損 540 太鬆(財報支撐在 569,低 5%)→ 多賠</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🟢 賠率2.85 持有</t>
+          <t>🔴 跌破停損價540(現價78.7)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
+          <t>🟠 負債比80% &gt; 80%(高槓桿)</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>183</v>
+        <v>182.5</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.06 持有</t>
+          <t>🟢 賠率2.14 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -889,64 +889,68 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42.9</v>
+        <v>215</v>
       </c>
       <c r="E7" t="n">
-        <v>43.99</v>
+        <v>236.26</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="G7" t="n">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>34.9</v>
+        <v>252.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36</v>
+        <v>252.6</v>
       </c>
       <c r="K7" t="n">
-        <v>34.9</v>
+        <v>292</v>
       </c>
       <c r="L7" t="n">
-        <v>36</v>
+        <v>232.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 200 太鬆(財報支撐在 253,低 21%)→ 多賠</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.11 考慮減碼</t>
+          <t>🟢 賠率2.33 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>🟠 負債比81% &gt; 70% 且流動比83% &lt; 100%(短期償債警報)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -955,19 +959,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>42.5</v>
       </c>
       <c r="E8" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F8" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -975,38 +979,34 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率12.33 持有</t>
+          <t>🟡 賠率1.67 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>148</v>
+        <v>145.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率8.00 持有</t>
+          <t>🟢 賠率11.46 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="E4" t="n">
         <v>305.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價288.0)</t>
+          <t>🔴 跌破停損價300(現價296.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78.7</v>
+        <v>78</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價78.7)</t>
+          <t>🔴 跌破停損價540(現價78.0)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>182.5</v>
+        <v>185</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.14 持有</t>
+          <t>🟡 賠率1.75 考慮減碼</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -869,7 +869,11 @@
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -889,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>215</v>
+        <v>218.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,14 +930,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.33 持有</t>
+          <t>🟡 賠率1.70 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -959,7 +963,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="E8" t="n">
         <v>43.99</v>
@@ -996,7 +1000,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.67 考慮減碼</t>
+          <t>🟡 賠率1.86 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1025,7 +1029,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>145.5</v>
+        <v>145</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1066,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率11.46 持有</t>
+          <t>🟢 賠率12.50 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>296</v>
+        <v>291.5</v>
       </c>
       <c r="E4" t="n">
         <v>305.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價296.0)</t>
+          <t>🔴 跌破停損價300(現價291.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價78.0)</t>
+          <t>🔴 跌破停損價540(現價75.9)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>185</v>
+        <v>186.5</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.75 考慮減碼</t>
+          <t>🟡 賠率1.56 考慮減碼</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>218.5</v>
+        <v>220</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -930,7 +930,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.70 考慮減碼</t>
+          <t>🟡 賠率1.50 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.4</v>
+        <v>42.8</v>
       </c>
       <c r="E8" t="n">
         <v>43.99</v>
@@ -1000,7 +1000,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.86 考慮減碼</t>
+          <t>🟡 賠率1.22 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1066,7 +1066,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率12.50 持有</t>
+          <t>🟢 賠率15.20 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>117.5</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.30&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.32&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>291.5</v>
+        <v>43.3</v>
       </c>
       <c r="E4" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,24 +703,24 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L4" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價291.5)</t>
+          <t>🟠 賠率0.74&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -730,11 +730,7 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價75.9)</t>
+          <t>🔴 跌破停損價540(現價74.5)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -809,72 +805,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>186.5</v>
+        <v>296</v>
       </c>
       <c r="E6" t="n">
-        <v>190.02</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>194</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>194</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>158.8</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>235.2</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.56 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
-        </is>
-      </c>
+          <t>🔴 跌破停損價300(現價296.0)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -893,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>220</v>
+        <v>223.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -930,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.50 考慮減碼</t>
+          <t>🟡 賠率1.13 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -949,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -963,51 +959,55 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.8</v>
+        <v>188</v>
       </c>
       <c r="E8" t="n">
-        <v>43.99</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>34.9</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>34.9</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.22 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>🟡 賠率1.39 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>144</v>
+        <v>142.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1066,7 +1066,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率15.20 持有</t>
+          <t>🟢 賠率22.14 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.32&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價74.5)</t>
+          <t>🔴 跌破停損價540(現價75.9)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>296</v>
+        <v>295.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價296.0)</t>
+          <t>🔴 跌破停損價300(現價295.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>188</v>
+        <v>188.5</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.39 考慮減碼</t>
+          <t>🟡 賠率1.34 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1066,7 +1066,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率22.14 持有</t>
+          <t>🟢 賠率17.00 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>123.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.30&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.3</v>
+        <v>292.5</v>
       </c>
       <c r="E4" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,24 +703,24 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.74&lt;1 應出場</t>
+          <t>🔴 跌破停損價300(現價292.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -730,7 +730,11 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價75.9)</t>
+          <t>🔴 跌破停損價540(現價74.9)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -805,72 +809,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>295.5</v>
+        <v>188.5</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>190.02</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>194</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>158.8</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>235.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價295.5)</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>🟡 賠率1.34 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223.5</v>
+        <v>224</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +930,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.13 考慮減碼</t>
+          <t>🟡 賠率1.08 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,12 +949,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,55 +963,51 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>188.5</v>
+        <v>42.6</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>43.99</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>34.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.34 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
-        </is>
-      </c>
+          <t>🟡 賠率1.50 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>143.5</v>
+        <v>144</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1066,7 +1066,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率17.00 持有</t>
+          <t>🟢 賠率15.20 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123.5</v>
+        <v>123</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.30&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>292.5</v>
+        <v>43.2</v>
       </c>
       <c r="E4" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,24 +703,24 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L4" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價292.5)</t>
+          <t>🟠 賠率0.82&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -730,11 +730,7 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價74.9)</t>
+          <t>🔴 跌破停損價540(現價74.8)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -809,72 +805,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>188.5</v>
+        <v>296</v>
       </c>
       <c r="E6" t="n">
-        <v>190.02</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>194</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>194</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>158.8</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>235.2</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟡 賠率1.34 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
-        </is>
-      </c>
+          <t>🔴 跌破停損價300(現價296.0)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -893,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -930,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.08 考慮減碼</t>
+          <t>🟡 賠率1.17 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -949,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -963,53 +959,53 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.6</v>
+        <v>179</v>
       </c>
       <c r="E8" t="n">
-        <v>43.99</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>34.9</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>34.9</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.50 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>🟢 賠率2.93 持有</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1029,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>144</v>
+        <v>151.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1066,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率15.20 持有</t>
+          <t>🟢 賠率5.48 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>122.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.33&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.2</v>
+        <v>300</v>
       </c>
       <c r="E4" t="n">
-        <v>43.99</v>
+        <v>305.63</v>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>340</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,24 +703,24 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36</v>
+        <v>166.7</v>
       </c>
       <c r="K4" t="n">
-        <v>34.9</v>
+        <v>244.6</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>145.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.82&lt;1 應出場</t>
+          <t>🔴 跌破停損價300(現價300.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -730,7 +730,11 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -749,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價74.8)</t>
+          <t>🔴 跌破停損價540(現價74.1)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -805,72 +809,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🔴 出場</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>296</v>
+        <v>179</v>
       </c>
       <c r="E6" t="n">
-        <v>305.63</v>
+        <v>190.02</v>
       </c>
       <c r="F6" t="n">
-        <v>340</v>
+        <v>220</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>165</v>
       </c>
       <c r="H6" t="n">
-        <v>244.6</v>
+        <v>194</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>166.7</v>
+        <v>194</v>
       </c>
       <c r="K6" t="n">
-        <v>244.6</v>
+        <v>158.8</v>
       </c>
       <c r="L6" t="n">
-        <v>145.3</v>
+        <v>235.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價296.0)</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>🟢 賠率2.93 持有</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>223</v>
+        <v>220.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.17 考慮減碼</t>
+          <t>🟡 賠率1.44 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,53 +959,53 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179</v>
+        <v>42.8</v>
       </c>
       <c r="E8" t="n">
-        <v>190.02</v>
+        <v>43.99</v>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>165</v>
+        <v>41</v>
       </c>
       <c r="H8" t="n">
-        <v>194</v>
+        <v>34.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>194</v>
+        <v>36</v>
       </c>
       <c r="K8" t="n">
-        <v>158.8</v>
+        <v>34.9</v>
       </c>
       <c r="L8" t="n">
-        <v>235.2</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.93 持有</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
-        </is>
-      </c>
+          <t>🟡 賠率1.22 考慮減碼</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>151.5</v>
+        <v>159.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率5.48 持有</t>
+          <t>🟢 賠率2.95 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122.5</v>
+        <v>121.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E4" t="n">
         <v>305.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價300.0)</t>
+          <t>🔴 跌破停損價300(現價296.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價74.1)</t>
+          <t>🔴 跌破停損價540(現價74.2)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.93 持有</t>
+          <t>🟢 賠率2.67 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>220.5</v>
+        <v>218.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.44 考慮減碼</t>
+          <t>🟡 賠率1.70 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
         <v>43.99</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.22 考慮減碼</t>
+          <t>🟡 賠率1.00 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>159.5</v>
+        <v>163.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.95 持有</t>
+          <t>🟢 賠率2.31 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.32&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E4" t="n">
         <v>305.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價296.0)</t>
+          <t>🔴 跌破停損價300(現價289.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.2</v>
+        <v>75</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價74.2)</t>
+          <t>🔴 跌破停損價540(現價75.0)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.67 持有</t>
+          <t>🟢 賠率2.24 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>218.5</v>
+        <v>216.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,14 +926,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.70 考慮減碼</t>
+          <t>🟢 賠率2.03 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,37 +959,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>179.5</v>
       </c>
       <c r="E8" t="n">
-        <v>43.99</v>
+        <v>160.86</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H8" t="n">
-        <v>34.9</v>
+        <v>138.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36</v>
+        <v>138.9</v>
       </c>
       <c r="K8" t="n">
-        <v>34.9</v>
+        <v>113</v>
       </c>
       <c r="L8" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1011,63 +1011,67 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>163.5</v>
+        <v>42.8</v>
       </c>
       <c r="E9" t="n">
-        <v>160.86</v>
+        <v>43.99</v>
       </c>
       <c r="F9" t="n">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>139</v>
+        <v>41</v>
       </c>
       <c r="H9" t="n">
-        <v>138.9</v>
+        <v>34.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>138.9</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>113</v>
+        <v>34.9</v>
       </c>
       <c r="L9" t="n">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.31 持有</t>
+          <t>🟡 賠率1.22 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>121.5</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>117</v>
+        <v>118.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.32&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>289</v>
+        <v>297.5</v>
       </c>
       <c r="E4" t="n">
         <v>305.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價289.0)</t>
+          <t>🔴 跌破停損價300(現價297.5)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>73.5</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價75.0)</t>
+          <t>🔴 跌破停損價540(現價73.5)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>182</v>
+        <v>179.5</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.24 持有</t>
+          <t>🟢 賠率2.79 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>216.5</v>
+        <v>216</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.03 持有</t>
+          <t>🟢 賠率2.12 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179.5</v>
+        <v>177</v>
       </c>
       <c r="E8" t="n">
         <v>160.86</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.00 考慮減碼</t>
+          <t>🟡 賠率1.13 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="E9" t="n">
         <v>43.99</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.22 考慮減碼</t>
+          <t>🟡 賠率1.11 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118.5</v>
+        <v>116</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.27&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>297.5</v>
+        <v>295</v>
       </c>
       <c r="E4" t="n">
         <v>305.63</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價297.5)</t>
+          <t>🔴 跌破停損價300(現價295.0)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +790,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價73.5)</t>
+          <t>🔴 跌破停損價540(現價73.4)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>179.5</v>
+        <v>182</v>
       </c>
       <c r="E6" t="n">
         <v>190.02</v>
@@ -860,7 +860,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.79 持有</t>
+          <t>🟢 賠率2.24 持有</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,14 +926,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.12 持有</t>
+          <t>🟡 賠率1.94 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="E8" t="n">
         <v>160.86</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.13 考慮減碼</t>
+          <t>🟡 賠率1.79 考慮減碼</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="E9" t="n">
         <v>43.99</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.11 考慮減碼</t>
+          <t>🟡 賠率1.22 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.35&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.46&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -669,12 +669,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>295</v>
+        <v>43.5</v>
       </c>
       <c r="E4" t="n">
-        <v>305.63</v>
+        <v>43.99</v>
       </c>
       <c r="F4" t="n">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="H4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -703,24 +703,24 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>166.7</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>244.6</v>
+        <v>34.9</v>
       </c>
       <c r="L4" t="n">
-        <v>145.3</v>
+        <v>36</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
+          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價295.0)</t>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -730,11 +730,7 @@
           <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -790,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價73.4)</t>
+          <t>🔴 跌破停損價540(現價70.6)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -809,68 +805,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 出場</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>182</v>
+        <v>290</v>
       </c>
       <c r="E6" t="n">
-        <v>190.02</v>
+        <v>305.63</v>
       </c>
       <c r="F6" t="n">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="G6" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>194</v>
+        <v>244.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PE法</t>
+          <t>PBR法</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>194</v>
+        <v>166.7</v>
       </c>
       <c r="K6" t="n">
-        <v>158.8</v>
+        <v>244.6</v>
       </c>
       <c r="L6" t="n">
-        <v>235.2</v>
+        <v>145.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
+          <t>⚠️ 手填停損 300 太緊(財報支撐在 245,高 23%)→ 易被洗出</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🟢 賠率2.24 持有</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
-        </is>
-      </c>
+          <t>🔴 跌破停損價300(現價290.0)</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>🟠 ROE 15 滑到5年均27的56%(&lt; 67%警戒)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>217</v>
+        <v>216.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,14 +926,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.94 考慮減碼</t>
+          <t>🟢 賠率2.03 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -945,12 +945,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -959,19 +959,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E8" t="n">
-        <v>160.86</v>
+        <v>190.02</v>
       </c>
       <c r="F8" t="n">
         <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="H8" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -979,99 +979,95 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>138.9</v>
+        <v>194</v>
       </c>
       <c r="K8" t="n">
-        <v>113</v>
+        <v>158.8</v>
       </c>
       <c r="L8" t="n">
-        <v>123</v>
+        <v>235.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>✅ 手填停損與財報支撐一致</t>
+          <t>⚠️ 手填停損 165 太鬆(財報支撐在 194,低 15%)→ 多賠</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟡 賠率1.79 考慮減碼</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>🟢 賠率2.67 持有</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟢 抱緊</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42.8</v>
+        <v>164.5</v>
       </c>
       <c r="E9" t="n">
-        <v>43.99</v>
+        <v>160.86</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>220</v>
       </c>
       <c r="G9" t="n">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="H9" t="n">
-        <v>34.9</v>
+        <v>138.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PBR法</t>
+          <t>PE法</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36</v>
+        <v>138.9</v>
       </c>
       <c r="K9" t="n">
-        <v>34.9</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>⚠️ 手填停損 41 太緊(財報支撐在 35,高 17%)→ 易被洗出</t>
+          <t>✅ 手填停損與財報支撐一致</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.22 考慮減碼</t>
+          <t>🟢 賠率2.18 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>121.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.46&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🟠 賠率0.90&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>70.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價70.6)</t>
+          <t>🔴 跌破停損價540(現價72.1)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>290</v>
+        <v>293.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價290.0)</t>
+          <t>🔴 跌破停損價300(現價293.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>216.5</v>
+        <v>216</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.03 持有</t>
+          <t>🟢 賠率2.12 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>179.5</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.67 持有</t>
+          <t>🟢 賠率2.79 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟢 抱緊</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>164.5</v>
+        <v>178</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,12 +1062,16 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.18 持有</t>
+          <t>🟡 賠率1.08 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>🟢 現價下不會買(賠率&lt;2)</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>121.5</v>
+        <v>122.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.46&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價72.1)</t>
+          <t>🔴 跌破停損價540(現價71.7)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>293.5</v>
+        <v>291.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價293.5)</t>
+          <t>🔴 跌破停損價300(現價291.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.12 持有</t>
+          <t>🟢 賠率2.33 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>178</v>
+        <v>171.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.08 考慮減碼</t>
+          <t>🟡 賠率1.49 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122.5</v>
+        <v>122</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>112.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.46&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.48&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.90&lt;1 應出場</t>
+          <t>🟠 賠率0.82&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>291.5</v>
+        <v>278</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價291.5)</t>
+          <t>🔴 跌破停損價300(現價278.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,14 +926,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟢 賠率2.33 持有</t>
+          <t>🟡 賠率1.94 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級)</t>
+          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179.5</v>
+        <v>179</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.79 持有</t>
+          <t>🟢 賠率2.93 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>171.5</v>
+        <v>168</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.49 考慮減碼</t>
+          <t>🟡 賠率1.79 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122</v>
+        <v>121.5</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.40&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>112.5</v>
+        <v>115</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.48&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.82&lt;1 應出場</t>
+          <t>🟠 賠率0.67&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價71.7)</t>
+          <t>🔴 跌破停損價540(現價72.9)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價278.0)</t>
+          <t>🔴 跌破停損價300(現價284.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>217</v>
+        <v>217.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.94 考慮減碼</t>
+          <t>🟡 賠率1.86 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>179</v>
+        <v>178.5</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,12 +996,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率2.93 持有</t>
+          <t>🟢 賠率3.07 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>🟡 月營收動能連2月降(13.3→10.8→10.4)</t>
+          <t>🟡 月營收動能連2月降(10.8→10.4→9.3)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>168</v>
+        <v>167.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.79 考慮減碼</t>
+          <t>🟡 賠率1.84 考慮減碼</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>121.5</v>
+        <v>121</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,12 +584,12 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.44&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.47&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>🟡 最新月YoY-15.4%轉負</t>
+          <t>🟡 最新月YoY-11.6%轉負</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.67&lt;1 應出場</t>
+          <t>🟠 賠率0.60&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價72.9)</t>
+          <t>🔴 跌破停損價540(現價71.5)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價284.0)</t>
+          <t>🔴 跌破停損價300(現價279.0)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>217.5</v>
+        <v>218.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,7 +926,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.86 考慮減碼</t>
+          <t>🟡 賠率1.70 考慮減碼</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>178.5</v>
+        <v>178</v>
       </c>
       <c r="E8" t="n">
         <v>190.02</v>
@@ -996,7 +996,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>🟢 賠率3.07 持有</t>
+          <t>🟢 賠率3.23 持有</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟢 抱緊</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>167.5</v>
+        <v>165</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,16 +1062,12 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟡 賠率1.84 考慮減碼</t>
+          <t>🟢 賠率2.12 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>🟢 現價下不會買(賠率&lt;2)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/賣出訊號監看.xlsx
+++ b/data/賣出訊號監看.xlsx
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
         <v>117.63</v>
@@ -584,7 +584,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>🔴 賠率0.47&lt;0.5 立刻賣</t>
+          <t>🟠 賠率0.56&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115</v>
+        <v>115.5</v>
       </c>
       <c r="E3" t="n">
         <v>111.6</v>
@@ -654,7 +654,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>🔴 賠率0.38&lt;0.5 立刻賣</t>
+          <t>🔴 賠率0.37&lt;0.5 立刻賣</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="E4" t="n">
         <v>43.99</v>
@@ -720,7 +720,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>🟠 賠率0.60&lt;1 應出場</t>
+          <t>🟠 賠率0.82&lt;1 應出場</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="E5" t="n">
         <v>636</v>
@@ -786,7 +786,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價540(現價71.5)</t>
+          <t>🔴 跌破停損價540(現價72.3)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>279</v>
+        <v>277.5</v>
       </c>
       <c r="E6" t="n">
         <v>305.63</v>
@@ -856,7 +856,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>🔴 跌破停損價300(現價279.0)</t>
+          <t>🔴 跌破停損價300(現價277.5)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>218.5</v>
+        <v>216.5</v>
       </c>
       <c r="E7" t="n">
         <v>236.26</v>
@@ -926,14 +926,14 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>🟡 賠率1.70 考慮減碼</t>
+          <t>🟢 賠率2.03 持有</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>🟢 現價下不會買(非A/B級、賠率&lt;2)</t>
+          <t>🟢 現價下不會買(非A/B級)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>165</v>
+        <v>164.5</v>
       </c>
       <c r="E9" t="n">
         <v>160.86</v>
@@ -1062,7 +1062,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>🟢 賠率2.12 持有</t>
+          <t>🟢 賠率2.18 持有</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
